--- a/data/trans_dic/P55$familiar-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiar-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,68; 27,74</t>
+          <t>12,41; 27,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,79; 33,7</t>
+          <t>17,27; 33,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,72; 39,71</t>
+          <t>22,69; 40,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,09; 66,78</t>
+          <t>49,54; 66,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,04; 34,76</t>
+          <t>21,84; 34,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,39; 39,36</t>
+          <t>27,24; 39,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,49; 38,21</t>
+          <t>23,92; 38,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57,57; 66,24</t>
+          <t>57,64; 66,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,21; 29,97</t>
+          <t>20,97; 30,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,63; 35,08</t>
+          <t>25,77; 35,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,06; 36,86</t>
+          <t>25,66; 37,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,46; 64,73</t>
+          <t>57,42; 65,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 44,33</t>
+          <t>5,44; 45,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,78</t>
+          <t>0,0; 32,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 39,81</t>
+          <t>7,83; 39,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,27; 55,58</t>
+          <t>31,79; 55,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,63</t>
+          <t>0,0; 39,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 49,91</t>
+          <t>7,13; 52,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 32,6</t>
+          <t>7,69; 32,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,99; 58,43</t>
+          <t>38,8; 58,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 30,44</t>
+          <t>3,65; 31,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 31,11</t>
+          <t>6,39; 31,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,03; 31,47</t>
+          <t>10,77; 30,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,79; 53,0</t>
+          <t>38,24; 53,46</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,48</t>
+          <t>0,0; 70,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 44,58</t>
+          <t>10,01; 47,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 49,1</t>
+          <t>14,17; 48,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,81</t>
+          <t>0,0; 33,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,59</t>
+          <t>0,0; 64,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,4</t>
+          <t>0,0; 55,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,5; 42,23</t>
+          <t>16,31; 42,53</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,96; 26,41</t>
+          <t>13,87; 28,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,57; 30,96</t>
+          <t>16,53; 31,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,51; 37,22</t>
+          <t>21,89; 36,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,51; 57,65</t>
+          <t>44,95; 57,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,56; 31,66</t>
+          <t>19,92; 31,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,12; 37,37</t>
+          <t>26,03; 36,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,88; 34,57</t>
+          <t>22,36; 34,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,83; 62,42</t>
+          <t>54,8; 62,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,01; 27,96</t>
+          <t>19,05; 28,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,57; 33,67</t>
+          <t>23,85; 32,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,15; 33,68</t>
+          <t>23,37; 33,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,81; 59,53</t>
+          <t>53,06; 59,62</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13064; 28581</t>
+          <t>12781; 28346</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22081; 41825</t>
+          <t>21432; 41932</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21233; 37111</t>
+          <t>21211; 37540</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49890; 65217</t>
+          <t>48383; 64773</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45367; 71544</t>
+          <t>44954; 70546</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68712; 98730</t>
+          <t>68322; 98882</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51075; 79692</t>
+          <t>49891; 80499</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>148352; 170692</t>
+          <t>148515; 171000</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62411; 92563</t>
+          <t>64762; 92935</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96119; 131549</t>
+          <t>96625; 133010</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75686; 111330</t>
+          <t>77494; 112684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>204157; 230020</t>
+          <t>204042; 231598</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>750; 6290</t>
+          <t>772; 6455</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6160</t>
+          <t>0; 6505</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1723; 9106</t>
+          <t>1791; 9146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13453; 23909</t>
+          <t>13675; 24033</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4809</t>
+          <t>0; 5301</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1519; 10558</t>
+          <t>1508; 11063</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4011; 16967</t>
+          <t>4002; 17083</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20765; 31938</t>
+          <t>21208; 31718</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>886; 8427</t>
+          <t>1011; 8642</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2686; 12807</t>
+          <t>2632; 13002</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8266; 23573</t>
+          <t>8066; 22938</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37887; 51774</t>
+          <t>37348; 52220</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6413</t>
+          <t>0; 6558</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1662; 6741</t>
+          <t>1514; 7202</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1815</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1603</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1955,27 +1955,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1875; 6867</t>
+          <t>1982; 6832</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 8125</t>
+          <t>0; 6909</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4167</t>
+          <t>0; 4174</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 7057</t>
+          <t>0; 6632</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4802; 12291</t>
+          <t>4746; 12380</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16410; 33428</t>
+          <t>17560; 35546</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24227; 45248</t>
+          <t>24159; 46071</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26123; 45209</t>
+          <t>26582; 44854</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>70896; 89815</t>
+          <t>70025; 89616</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45180; 73115</t>
+          <t>45999; 73873</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72212; 103305</t>
+          <t>71946; 102179</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58493; 92435</t>
+          <t>59795; 92871</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>178916; 203703</t>
+          <t>178816; 203392</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67956; 99972</t>
+          <t>68120; 100743</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103809; 142298</t>
+          <t>100784; 139212</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93890; 130956</t>
+          <t>90859; 129260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>254624; 287018</t>
+          <t>255822; 287415</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$familiar-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiar-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,41; 27,51</t>
+          <t>12,22; 27,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,27; 33,78</t>
+          <t>17,38; 33,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,69; 40,16</t>
+          <t>22,5; 40,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,54; 66,33</t>
+          <t>50,38; 66,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,84; 34,27</t>
+          <t>22,01; 35,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,24; 39,42</t>
+          <t>26,93; 39,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,92; 38,6</t>
+          <t>24,28; 38,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57,64; 66,36</t>
+          <t>56,84; 65,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,97; 30,09</t>
+          <t>20,14; 30,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,77; 35,47</t>
+          <t>25,47; 35,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,66; 37,31</t>
+          <t>25,21; 36,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,42; 65,18</t>
+          <t>56,92; 64,56</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 45,49</t>
+          <t>5,62; 40,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,5</t>
+          <t>0,0; 31,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,83; 39,98</t>
+          <t>10,27; 41,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,79; 55,87</t>
+          <t>29,68; 53,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,27</t>
+          <t>0,0; 33,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 52,3</t>
+          <t>5,44; 47,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,69; 32,83</t>
+          <t>7,76; 32,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,8; 58,03</t>
+          <t>37,18; 55,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 31,21</t>
+          <t>3,36; 31,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 31,58</t>
+          <t>6,19; 31,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,77; 30,62</t>
+          <t>10,36; 30,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,24; 53,46</t>
+          <t>37,59; 51,9</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,02</t>
+          <t>0,0; 69,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,16</t>
+          <t>0,0; 78,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 47,63</t>
+          <t>7,93; 43,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,17; 48,85</t>
+          <t>13,78; 51,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,0</t>
+          <t>0,0; 39,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,69</t>
+          <t>0,0; 65,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,83</t>
+          <t>0,0; 57,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,31; 42,53</t>
+          <t>16,11; 40,89</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,87; 28,08</t>
+          <t>13,68; 27,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,53; 31,52</t>
+          <t>16,22; 31,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,89; 36,93</t>
+          <t>21,9; 36,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,95; 57,52</t>
+          <t>43,67; 56,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,92; 31,99</t>
+          <t>19,9; 31,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,03; 36,97</t>
+          <t>25,87; 37,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,36; 34,74</t>
+          <t>22,32; 34,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,8; 62,33</t>
+          <t>53,47; 61,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,05; 28,18</t>
+          <t>19,27; 28,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,85; 32,94</t>
+          <t>24,37; 33,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,37; 33,24</t>
+          <t>23,35; 33,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,06; 59,62</t>
+          <t>51,84; 58,46</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57673</t>
+          <t>60551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>160118</t>
+          <t>170461</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>217791</t>
+          <t>231012</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12781; 28346</t>
+          <t>12591; 28236</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21432; 41932</t>
+          <t>21568; 41394</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21211; 37540</t>
+          <t>21029; 38016</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48383; 64773</t>
+          <t>52279; 68665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44954; 70546</t>
+          <t>45302; 72648</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68322; 98882</t>
+          <t>67544; 99139</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49891; 80499</t>
+          <t>50635; 79258</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>148515; 171000</t>
+          <t>157331; 182663</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64762; 92935</t>
+          <t>62199; 93597</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96625; 133010</t>
+          <t>95520; 132582</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77494; 112684</t>
+          <t>76153; 109517</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>204042; 231598</t>
+          <t>216638; 245711</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>20072</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26572</t>
+          <t>29065</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45178</t>
+          <t>49138</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>772; 6455</t>
+          <t>798; 5815</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6505</t>
+          <t>0; 6363</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1791; 9146</t>
+          <t>2349; 9443</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13675; 24033</t>
+          <t>14047; 25311</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5301</t>
+          <t>0; 4499</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1508; 11063</t>
+          <t>1150; 10143</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4002; 17083</t>
+          <t>4037; 17149</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21208; 31718</t>
+          <t>23292; 35054</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1011; 8642</t>
+          <t>929; 8612</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2632; 13002</t>
+          <t>2549; 12997</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8066; 22938</t>
+          <t>7763; 23008</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37348; 52220</t>
+          <t>41342; 57083</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>8480</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6558</t>
+          <t>0; 6480</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3489</t>
+          <t>0; 3998</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1514; 7202</t>
+          <t>1314; 7208</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1955,27 +1955,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1982; 6832</t>
+          <t>2170; 8042</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6909</t>
+          <t>0; 8238</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4174</t>
+          <t>0; 4205</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6632</t>
+          <t>0; 6823</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4746; 12380</t>
+          <t>5207; 13216</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80093</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>190866</t>
+          <t>204183</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>270958</t>
+          <t>288630</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17560; 35546</t>
+          <t>17321; 35325</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24159; 46071</t>
+          <t>23707; 45501</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26582; 44854</t>
+          <t>26604; 44783</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>70025; 89616</t>
+          <t>73227; 95062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45999; 73873</t>
+          <t>45953; 73648</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71946; 102179</t>
+          <t>71514; 103717</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59795; 92871</t>
+          <t>59683; 92419</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>178816; 203392</t>
+          <t>189936; 217556</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68120; 100743</t>
+          <t>68901; 101870</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100784; 139212</t>
+          <t>102990; 142433</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>90859; 129260</t>
+          <t>90803; 128435</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>255822; 287415</t>
+          <t>271044; 305669</t>
         </is>
       </c>
     </row>
